--- a/呉俊鋒_週報_2025年9月分.xlsx
+++ b/呉俊鋒_週報_2025年9月分.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D8F43D-D7C4-4251-9D61-BCFA53C54437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA0D70A-F592-4000-B3EE-0D585332E1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年9月1日の週" sheetId="6" r:id="rId1"/>
+    <sheet name="2025年9月8日の週" sheetId="7" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="Holiday">[1]祝日!$A$2:$B$335</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2025年9月1日の週'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2025年9月8日の週'!$A$1:$K$20</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>所属</t>
     <rPh sb="0" eb="2">
@@ -158,6 +160,80 @@
     </rPh>
     <rPh sb="74" eb="76">
       <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・9/8
+　■佐藤社長から送ったイメージを参照して、製品らしく調整した
+・9/9
+　■佐藤社長から送ったイメージを参照して、製品らしく調整した
+　　製品らしく調整したものを佐藤社長に報告した
+・9/10
+　■ブルートゥースでデータ転送調査
+・9/11
+　■ブルートゥースでデータ転送調査
+　　クライアント作成必要かも
+・9/12
+　■ブルートゥースでデータ転送調査
+　　クライアントを作成したが、M5Stack側まだ調査中
+　■山口県に出張して、M5Stackとセンサーをカバーにおいて、佐藤社長に報告した</t>
+    <rPh sb="7" eb="11">
+      <t>サトウシャチョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="86" eb="90">
+      <t>サトウシャチョウ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="152" eb="154">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="192" eb="194">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="205" eb="206">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="208" eb="211">
+      <t>チョウサチュウ</t>
+    </rPh>
+    <rPh sb="214" eb="217">
+      <t>ヤマグチケン</t>
+    </rPh>
+    <rPh sb="218" eb="220">
+      <t>シュッチョウ</t>
+    </rPh>
+    <rPh sb="244" eb="246">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>シャチョウ</t>
+    </rPh>
+    <rPh sb="249" eb="251">
+      <t>ホウコク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3878,4 +3954,308 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3519A8DA-D9BA-482D-88B4-4FA90873F74E}">
+  <dimension ref="B1:M20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="7.8984375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="16.3984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.09765625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B4" s="13"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B5" s="13"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B6" s="13"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B7" s="13"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="2:13" ht="364.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="30"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B10" s="13"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B12" s="13"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="2:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B15" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B16" s="13"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" s="13"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" s="13"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="2:11" ht="147.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="14"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:K20"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:K8"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>